--- a/public/templates/tool.xlsx
+++ b/public/templates/tool.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AJ1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,84 +430,90 @@
         <v>严重度*</v>
       </c>
       <c r="J1" t="str">
-        <v>对应归因*</v>
+        <v>对应归因编码*</v>
       </c>
       <c r="K1" t="str">
+        <v>对应归因名称</v>
+      </c>
+      <c r="L1" t="str">
         <v>工具标签*</v>
       </c>
-      <c r="L1" t="str">
-        <v>作用维度</v>
-      </c>
       <c r="M1" t="str">
+        <v>作用维度编码</v>
+      </c>
+      <c r="N1" t="str">
+        <v>效果说明</v>
+      </c>
+      <c r="O1" t="str">
         <v>操作步骤摘要*</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>关键话术</v>
       </c>
-      <c r="O1" t="str">
+      <c r="Q1" t="str">
         <v>预期效果*</v>
       </c>
-      <c r="P1" t="str">
+      <c r="R1" t="str">
         <v>单次耗时</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="S1" t="str">
         <v>疗程与频次</v>
       </c>
-      <c r="R1" t="str">
+      <c r="T1" t="str">
         <v>重评间隔天数</v>
       </c>
-      <c r="S1" t="str">
+      <c r="U1" t="str">
         <v>禁止事项*</v>
       </c>
-      <c r="T1" t="str">
+      <c r="V1" t="str">
         <v>禁忌说明</v>
       </c>
-      <c r="U1" t="str">
+      <c r="W1" t="str">
         <v>前置工具编码</v>
       </c>
-      <c r="V1" t="str">
+      <c r="X1" t="str">
         <v>替代工具编码</v>
       </c>
-      <c r="W1" t="str">
+      <c r="Y1" t="str">
         <v>进阶工具编码</v>
       </c>
-      <c r="X1" t="str">
+      <c r="Z1" t="str">
         <v>证据等级*</v>
       </c>
-      <c r="Y1" t="str">
+      <c r="AA1" t="str">
         <v>证据来源</v>
       </c>
-      <c r="Z1" t="str">
+      <c r="AB1" t="str">
         <v>效果指标</v>
       </c>
-      <c r="AA1" t="str">
+      <c r="AC1" t="str">
         <v>失败标准</v>
       </c>
-      <c r="AB1" t="str">
+      <c r="AD1" t="str">
         <v>准备事项</v>
       </c>
-      <c r="AC1" t="str">
+      <c r="AE1" t="str">
         <v>所需材料</v>
       </c>
-      <c r="AD1" t="str">
+      <c r="AF1" t="str">
         <v>输出物</v>
       </c>
-      <c r="AE1" t="str">
+      <c r="AG1" t="str">
         <v>协同工具编码</v>
       </c>
-      <c r="AF1" t="str">
+      <c r="AH1" t="str">
         <v>手册出处*</v>
       </c>
-      <c r="AG1" t="str">
+      <c r="AI1" t="str">
         <v>版本*</v>
       </c>
-      <c r="AH1" t="str">
+      <c r="AJ1" t="str">
         <v>跨模块标签</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AH1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AJ1"/>
   </ignoredErrors>
 </worksheet>
 </file>
